--- a/artfynd/A 33757-2023 artfynd.xlsx
+++ b/artfynd/A 33757-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33757-2023 artfynd.xlsx
+++ b/artfynd/A 33757-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55296654</v>
+        <v>667018</v>
       </c>
       <c r="B2" t="n">
-        <v>57140</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,58 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100088</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bokbacken, Getinge, Hl</t>
+          <t>Ö LASSARED (05C0c08), Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363808.1190391334</v>
+        <v>363974</v>
       </c>
       <c r="R2" t="n">
-        <v>6300271.056555969</v>
+        <v>6300424</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-09-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>1994-06-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>1994-06-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>050202081 / HOMA SER / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,23 +762,165 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Lövskog i branter</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gammal grov ek</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Jesper Lind</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>55296654</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bokbacken, Getinge, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>363808</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6300271</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Getinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-09-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-09-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Lövskog i branter</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Peter Aksberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Peter Aksberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33757-2023 artfynd.xlsx
+++ b/artfynd/A 33757-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/667018</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,8 +931,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55296654</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>